--- a/artfynd/A 40906-2026 artfynd.xlsx
+++ b/artfynd/A 40906-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137326120</v>
       </c>
       <c r="B2" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>137326119</v>
       </c>
       <c r="B3" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>137326123</v>
       </c>
       <c r="B4" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40906-2026 artfynd.xlsx
+++ b/artfynd/A 40906-2026 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>137326119</v>
       </c>
       <c r="B3" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>137326123</v>
       </c>
       <c r="B4" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40906-2026 artfynd.xlsx
+++ b/artfynd/A 40906-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137326120</v>
       </c>
       <c r="B2" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>137326119</v>
       </c>
       <c r="B3" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>137326123</v>
       </c>
       <c r="B4" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40906-2026 artfynd.xlsx
+++ b/artfynd/A 40906-2026 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>137326119</v>
       </c>
       <c r="B3" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>137326123</v>
       </c>
       <c r="B4" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40906-2026 artfynd.xlsx
+++ b/artfynd/A 40906-2026 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>137326119</v>
       </c>
       <c r="B3" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>137326123</v>
       </c>
       <c r="B4" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40906-2026 artfynd.xlsx
+++ b/artfynd/A 40906-2026 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>137326119</v>
       </c>
       <c r="B3" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>137326123</v>
       </c>
       <c r="B4" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40906-2026 artfynd.xlsx
+++ b/artfynd/A 40906-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137326120</v>
       </c>
       <c r="B2" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>137326119</v>
       </c>
       <c r="B3" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>137326123</v>
       </c>
       <c r="B4" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
